--- a/docs/downloads/ThongTinChungQuyen_latest.xlsx
+++ b/docs/downloads/ThongTinChungQuyen_latest.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPBank ( LPS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPBank ( LPS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPBank ( LPS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPBank ( LPS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPBank ( LPS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPBank ( LPS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPBank ( LPS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán LPBank ( LPS )</t>
+          <t>CTCP Chứng khoán LPS ( LPS )</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">

--- a/docs/downloads/ThongTinChungQuyen_latest.xlsx
+++ b/docs/downloads/ThongTinChungQuyen_latest.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>CTCP Chứng khoán KAFI ( KAFI )</t>
+          <t>CTCP Chứng khoán KAFI ( KAI )</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
